--- a/rtos-api-analysis/results/runtime/threadx-6.4.2_elapsed_time_summary.xlsx
+++ b/rtos-api-analysis/results/runtime/threadx-6.4.2_elapsed_time_summary.xlsx
@@ -492,28 +492,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5874.966666666666</v>
+        <v>4517.96875</v>
       </c>
       <c r="C2" t="n">
-        <v>99.57570621468926</v>
+        <v>48.06349734042553</v>
       </c>
       <c r="D2" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>236.7934855968219</v>
+        <v>122.0735085911381</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>1442</v>
+        <v>832</v>
       </c>
       <c r="H2" t="n">
-        <v>59</v>
+        <v>94</v>
       </c>
       <c r="I2" t="n">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>

--- a/rtos-api-analysis/results/runtime/threadx-6.4.2_elapsed_time_summary.xlsx
+++ b/rtos-api-analysis/results/runtime/threadx-6.4.2_elapsed_time_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,52 +436,77 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>SourceTable</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Total(s)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Mean(s)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Median(s)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Median(min)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Standard Deviation(s)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Minimum(s)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Maximum(s)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Completed API Count</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>All API Count</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>&gt; 1-Hour</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>&gt; 30-Minutes</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>StoppedByMaxTime_yes</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>StoppedByMaxTime_no</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>StoppedByMaxTime_unknown</t>
         </is>
       </c>
     </row>
@@ -491,34 +516,51 @@
           <t>threadx-6.4.2</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>4517.96875</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>walltime</t>
+        </is>
       </c>
       <c r="C2" t="n">
-        <v>48.06349734042553</v>
+        <v>37116.5024</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>386.6302333333333</v>
       </c>
       <c r="E2" t="n">
-        <v>122.0735085911381</v>
+        <v>2.63175</v>
       </c>
       <c r="F2" t="n">
+        <v>0.04386250000000001</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3673.185355544855</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="I2" t="n">
+        <v>36000.4091</v>
+      </c>
+      <c r="J2" t="n">
+        <v>96</v>
+      </c>
+      <c r="K2" t="n">
+        <v>96</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" t="n">
         <v>0</v>
       </c>
-      <c r="G2" t="n">
-        <v>832</v>
-      </c>
-      <c r="H2" t="n">
-        <v>94</v>
-      </c>
-      <c r="I2" t="n">
-        <v>97</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
+      <c r="O2" t="n">
+        <v>96</v>
+      </c>
+      <c r="P2" t="n">
         <v>0</v>
       </c>
     </row>
